--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743954</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>122743952</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743954</v>
+        <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattesmyran Ö, Hls</t>
+          <t>system NV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565213</v>
+        <v>565204</v>
       </c>
       <c r="R2" t="n">
-        <v>6883802</v>
+        <v>6883790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743952</v>
+        <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,38 +793,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565204</v>
+        <v>565213</v>
       </c>
       <c r="R3" t="n">
-        <v>6883790</v>
+        <v>6883802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743952</v>
+        <v>122743954</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565204</v>
+        <v>565213</v>
       </c>
       <c r="R2" t="n">
-        <v>6883790</v>
+        <v>6883802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743954</v>
+        <v>122743952</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +807,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mattesmyran Ö, Hls</t>
+          <t>system NV, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565213</v>
+        <v>565204</v>
       </c>
       <c r="R3" t="n">
-        <v>6883802</v>
+        <v>6883790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 planta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743954</v>
+        <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattesmyran Ö, Hls</t>
+          <t>system NV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565213</v>
+        <v>565204</v>
       </c>
       <c r="R2" t="n">
-        <v>6883802</v>
+        <v>6883790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743952</v>
+        <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,38 +793,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565204</v>
+        <v>565213</v>
       </c>
       <c r="R3" t="n">
-        <v>6883790</v>
+        <v>6883802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743952</v>
+        <v>122743954</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565204</v>
+        <v>565213</v>
       </c>
       <c r="R2" t="n">
-        <v>6883790</v>
+        <v>6883802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743954</v>
+        <v>122743952</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +807,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mattesmyran Ö, Hls</t>
+          <t>system NV, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565213</v>
+        <v>565204</v>
       </c>
       <c r="R3" t="n">
-        <v>6883802</v>
+        <v>6883790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 planta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743954</v>
+        <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattesmyran Ö, Hls</t>
+          <t>system NV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565213</v>
+        <v>565204</v>
       </c>
       <c r="R2" t="n">
-        <v>6883802</v>
+        <v>6883790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743952</v>
+        <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,38 +793,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565204</v>
+        <v>565213</v>
       </c>
       <c r="R3" t="n">
-        <v>6883790</v>
+        <v>6883802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743952</v>
+        <v>122743954</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565204</v>
+        <v>565213</v>
       </c>
       <c r="R2" t="n">
-        <v>6883790</v>
+        <v>6883802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743954</v>
+        <v>122743952</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +807,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mattesmyran Ö, Hls</t>
+          <t>system NV, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565213</v>
+        <v>565204</v>
       </c>
       <c r="R3" t="n">
-        <v>6883802</v>
+        <v>6883790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 planta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743954</v>
+        <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattesmyran Ö, Hls</t>
+          <t>system NV, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565213</v>
+        <v>565204</v>
       </c>
       <c r="R2" t="n">
-        <v>6883802</v>
+        <v>6883790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743952</v>
+        <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,38 +793,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565204</v>
+        <v>565213</v>
       </c>
       <c r="R3" t="n">
-        <v>6883790</v>
+        <v>6883802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,12 +765,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -784,12 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,6 +814,9 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mattesmyran Ö, Hls</t>
@@ -879,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,12 +884,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743952</v>
       </c>
       <c r="B2" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122743954</v>
       </c>
       <c r="B3" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33608-2024 artfynd.xlsx
+++ b/artfynd/A 33608-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743952</v>
+        <v>122743947</v>
       </c>
       <c r="B2" t="n">
-        <v>79332</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>system NV, Hls</t>
+          <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565204</v>
+        <v>565172</v>
       </c>
       <c r="R2" t="n">
-        <v>6883790</v>
+        <v>6883668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743954</v>
+        <v>122743946</v>
       </c>
       <c r="B3" t="n">
-        <v>99125</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,46 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mattesmyran Ö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565213</v>
+        <v>565241</v>
       </c>
       <c r="R3" t="n">
-        <v>6883802</v>
+        <v>6883929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,18 +853,12 @@
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 planta</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,6 +874,226 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122743952</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>system NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565204</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6883790</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122743954</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mattesmyran Ö, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565213</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6883802</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 planta</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
